--- a/basedatos_partidas/salida/descompuestos/CT-08-06-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-06-020.xlsx
@@ -539,10 +539,10 @@
         <v>0.095</v>
       </c>
       <c r="G10" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H10" t="n">
-        <v>10.93</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>1.08</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.54</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="12">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>22.63</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="17">
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>29.56</v>
+        <v>29.32</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>29.86</v>
+        <v>29.61</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-06-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-06-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos continuos de concreto y microcemento</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
